--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,236 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120093072</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>468331</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6546835</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>120092950</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57310</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>468305</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6546611</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120093072</v>
+        <v>120092950</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -841,14 +841,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468331</v>
+        <v>468305</v>
       </c>
       <c r="R3" t="n">
-        <v>6546835</v>
+        <v>6546611</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
+          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120092950</v>
+        <v>120093072</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -956,14 +956,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468305</v>
+        <v>468331</v>
       </c>
       <c r="R4" t="n">
-        <v>6546611</v>
+        <v>6546835</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
+          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120092950</v>
+        <v>120093072</v>
       </c>
       <c r="B3" t="n">
         <v>57310</v>
@@ -841,14 +841,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468305</v>
+        <v>468331</v>
       </c>
       <c r="R3" t="n">
-        <v>6546611</v>
+        <v>6546835</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
+          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120093072</v>
+        <v>120092950</v>
       </c>
       <c r="B4" t="n">
         <v>57310</v>
@@ -956,14 +956,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468331</v>
+        <v>468305</v>
       </c>
       <c r="R4" t="n">
-        <v>6546835</v>
+        <v>6546611</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
+          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -800,7 +800,7 @@
         <v>120093072</v>
       </c>
       <c r="B3" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>120092950</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -797,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120093072</v>
+        <v>120092950</v>
       </c>
       <c r="B3" t="n">
         <v>57320</v>
@@ -841,14 +841,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468331</v>
+        <v>468305</v>
       </c>
       <c r="R3" t="n">
-        <v>6546835</v>
+        <v>6546611</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
+          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120092950</v>
+        <v>120093072</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -956,14 +956,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468305</v>
+        <v>468331</v>
       </c>
       <c r="R4" t="n">
-        <v>6546611</v>
+        <v>6546835</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
+          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1025,6 +1025,118 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128525158</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Edsbacken N, Edsbacken N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>468235</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6546696</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall (tills m äldre ringhack) Ö sidan av vägen, 5m från vägen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>David Tverling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>128525158</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>128525158</v>
       </c>
       <c r="B5" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>128525158</v>
       </c>
       <c r="B5" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -1030,7 +1030,7 @@
         <v>128525158</v>
       </c>
       <c r="B5" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>115630946</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -716,7 +711,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edsbacken (Edsbacken), Nrk</t>
+          <t>Edsbacken, Edsbacken, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -797,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120093072</v>
+        <v>120092950</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,14 +831,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468331</v>
+        <v>468305</v>
       </c>
       <c r="R3" t="n">
-        <v>6546835</v>
+        <v>6546611</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,7 +875,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
+          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120092950</v>
+        <v>120093072</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -956,14 +941,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svartå Åtorpskorset SO, Atlasruta 09E9e (Edsbacken), Nrk</t>
+          <t>Svartå Åtorpskorset O, Atlasruta 09E9e (Edsbacken), Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468305</v>
+        <v>468331</v>
       </c>
       <c r="R4" t="n">
-        <v>6546611</v>
+        <v>6546835</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,7 +985,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska spår på en sida och äldre spår på den andra.  På tall</t>
+          <t>Färska hackringar på en tall som står söder om en gammal tall med bohål i</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,7 +1015,7 @@
         <v>128525158</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,6 +1121,218 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>117878228</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rultamon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>468233</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6546797</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>117878230</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rultamon, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>468233</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546797</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12720-2024 artfynd.xlsx
+++ b/artfynd/A 12720-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115630946</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128525158</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117878228</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1113,6 +1133,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117878230</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120092950</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,8 +1363,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120093072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>